--- a/data/trans_camb/PCS12_SP_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 14,87</t>
+          <t>-1,95; 14,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 9,68</t>
+          <t>-8,2; 9,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 25,32</t>
+          <t>5,55; 24,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 7,46</t>
+          <t>-10,35; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 6,35</t>
+          <t>-11,47; 6,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,6; 30,68</t>
+          <t>15,39; 30,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 8,66</t>
+          <t>-3,83; 8,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 5,58</t>
+          <t>-7,37; 4,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 25,42</t>
+          <t>12,6; 25,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 36,85</t>
+          <t>-3,99; 34,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 24,75</t>
+          <t>-16,87; 24,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 64,11</t>
+          <t>12,18; 61,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 14,51</t>
+          <t>-16,99; 16,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 12,03</t>
+          <t>-18,5; 12,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,01; 60,3</t>
+          <t>24,53; 58,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 18,54</t>
+          <t>-7,05; 17,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 11,75</t>
+          <t>-13,87; 10,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,64; 54,48</t>
+          <t>23,6; 53,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 8,16</t>
+          <t>-4,65; 8,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 3,32</t>
+          <t>-9,99; 3,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 3,8</t>
+          <t>-10,87; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 10,93</t>
+          <t>-0,88; 11,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 1,02</t>
+          <t>-11,57; 0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 2,98</t>
+          <t>-8,04; 2,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 7,97</t>
+          <t>-1,24; 7,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -0,15</t>
+          <t>-8,94; 0,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,42</t>
+          <t>-8,57; 0,93</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 17,7</t>
+          <t>-8,82; 19,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 7,29</t>
+          <t>-19,08; 8,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 8,45</t>
+          <t>-21,11; 7,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 19,82</t>
+          <t>-1,47; 21,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 1,79</t>
+          <t>-18,57; 1,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 4,95</t>
+          <t>-13,16; 4,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 15,54</t>
+          <t>-2,24; 14,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -0,35</t>
+          <t>-15,91; 0,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 2,82</t>
+          <t>-15,09; 1,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 8,31</t>
+          <t>-7,88; 7,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -4,79</t>
+          <t>-18,94; -4,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 17,9</t>
+          <t>2,72; 18,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,15; -9,36</t>
+          <t>-24,32; -9,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,95; -29,07</t>
+          <t>-42,59; -28,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,5; -10,18</t>
+          <t>-24,03; -10,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -2,99</t>
+          <t>-14,32; -2,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -19,06</t>
+          <t>-29,38; -19,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 1,39</t>
+          <t>-9,4; 1,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 21,81</t>
+          <t>-17,1; 20,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,78; -12,4</t>
+          <t>-42,07; -12,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 45,97</t>
+          <t>5,8; 48,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,64; -14,34</t>
+          <t>-34,06; -14,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,74; -42,99</t>
+          <t>-58,99; -43,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,51; -15,66</t>
+          <t>-33,55; -15,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -6,06</t>
+          <t>-24,12; -5,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,76; -35,39</t>
+          <t>-50,71; -35,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 2,57</t>
+          <t>-16,06; 2,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 3,86</t>
+          <t>-11,39; 3,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 21,86</t>
+          <t>7,87; 23,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 17,74</t>
+          <t>-0,96; 16,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -3,14</t>
+          <t>-16,38; -2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 10,3</t>
+          <t>-3,95; 10,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,77; -6,78</t>
+          <t>-36,53; -5,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -1,73</t>
+          <t>-11,62; -1,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 14,14</t>
+          <t>4,09; 14,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 1,78</t>
+          <t>-18,11; 2,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 10,11</t>
+          <t>-25,18; 10,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,93; 60,3</t>
+          <t>17,7; 60,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 47,51</t>
+          <t>-2,29; 42,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -5,3</t>
+          <t>-25,96; -4,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 18,38</t>
+          <t>-6,2; 18,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,11; -11,97</t>
+          <t>-58,21; -9,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,21; -3,52</t>
+          <t>-21,69; -3,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 29,27</t>
+          <t>7,75; 30,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 3,48</t>
+          <t>-37,27; 3,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 19,89</t>
+          <t>0,39; 21,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 6,86</t>
+          <t>-11,87; 6,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 15,96</t>
+          <t>-1,29; 16,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 19,31</t>
+          <t>-0,4; 19,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 0,09</t>
+          <t>-18,87; 0,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 12,44</t>
+          <t>-4,82; 11,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 16,73</t>
+          <t>3,68; 16,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,94; -0,09</t>
+          <t>-13,34; -0,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 12,23</t>
+          <t>-0,11; 12,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2,64; 70,09</t>
+          <t>0,47; 74,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 23,9</t>
+          <t>-30,49; 24,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 54,74</t>
+          <t>-4,21; 56,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 44,33</t>
+          <t>-0,73; 45,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 0,51</t>
+          <t>-36,4; 0,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 28,75</t>
+          <t>-8,65; 26,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,33; 45,09</t>
+          <t>8,26; 42,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,19; -0,37</t>
+          <t>-29,15; -0,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 32,44</t>
+          <t>-0,42; 32,18</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 13,08</t>
+          <t>-4,91; 12,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -0,03</t>
+          <t>-16,93; 0,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,03; 19,42</t>
+          <t>3,75; 19,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-22,2; -5,15</t>
+          <t>-20,42; -4,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-31,59; -14,9</t>
+          <t>-31,32; -14,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 0,99</t>
+          <t>-13,53; 0,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 1,26</t>
+          <t>-10,59; 1,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -9,85</t>
+          <t>-21,64; -10,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 7,94</t>
+          <t>-3,37; 7,95</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 32,47</t>
+          <t>-10,15; 33,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 0,09</t>
+          <t>-36,02; 0,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6,48; 49,73</t>
+          <t>8,08; 51,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,36; -7,87</t>
+          <t>-28,85; -7,24</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,16; -23,37</t>
+          <t>-43,45; -22,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 1,45</t>
+          <t>-18,75; 1,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 2,37</t>
+          <t>-17,94; 2,48</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,92; -18,5</t>
+          <t>-36,77; -18,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 14,99</t>
+          <t>-5,69; 14,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 1,84</t>
+          <t>-9,51; 1,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,76; -1,34</t>
+          <t>-13,04; -1,86</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 8,82</t>
+          <t>-3,34; 9,34</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 1,43</t>
+          <t>-9,29; 1,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -2,38</t>
+          <t>-13,09; -2,02</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 29,28</t>
+          <t>-7,27; 27,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,09</t>
+          <t>-7,81; -0,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,52; -3,62</t>
+          <t>-11,24; -3,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 25,88</t>
+          <t>-2,94; 23,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 4,07</t>
+          <t>-19,86; 3,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,51; -3,07</t>
+          <t>-26,72; -4,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 20,31</t>
+          <t>-7,01; 21,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 2,63</t>
+          <t>-15,34; 2,33</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,38; -4,44</t>
+          <t>-22,12; -3,8</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 52,34</t>
+          <t>-12,52; 51,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,86; -0,19</t>
+          <t>-14,74; -0,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,48; -7,07</t>
+          <t>-21,28; -7,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 51,9</t>
+          <t>-5,7; 46,76</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,57</t>
+          <t>-1,97; 8,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -1,19</t>
+          <t>-11,54; -1,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 38,57</t>
+          <t>-8,43; 39,1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 7,7</t>
+          <t>-2,57; 7,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,35</t>
+          <t>-9,38; 0,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-11,16; -1,35</t>
+          <t>-10,82; -1,43</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,85</t>
+          <t>-0,58; 6,53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -2,15</t>
+          <t>-9,41; -2,2</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 23,12</t>
+          <t>-7,52; 25,87</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 24,17</t>
+          <t>-5,08; 23,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,34; -2,84</t>
+          <t>-27,86; -3,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 104,83</t>
+          <t>-21,85; 104,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 17,39</t>
+          <t>-5,15; 17,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 0,79</t>
+          <t>-19,0; 1,44</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-22,35; -3,05</t>
+          <t>-22,04; -3,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 16,68</t>
+          <t>-1,29; 16,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -5,32</t>
+          <t>-20,99; -5,32</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 53,45</t>
+          <t>-17,33; 61,25</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,77</t>
+          <t>-0,97; 3,93</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -1,13</t>
+          <t>-6,05; -1,24</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,64; 19,39</t>
+          <t>2,56; 17,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,3</t>
+          <t>-5,05; -0,07</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -6,83</t>
+          <t>-11,47; -6,64</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 6,39</t>
+          <t>-6,17; 5,95</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,06</t>
+          <t>-2,46; 0,96</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -4,81</t>
+          <t>-8,14; -4,78</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,91</t>
+          <t>-0,96; 9,1</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 9,16</t>
+          <t>-2,2; 9,51</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -2,73</t>
+          <t>-13,79; -2,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6,17; 46,13</t>
+          <t>5,88; 41,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -0,55</t>
+          <t>-8,72; -0,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-20,12; -12,3</t>
+          <t>-19,76; -11,82</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 11,3</t>
+          <t>-10,94; 10,58</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,17</t>
+          <t>-4,85; 1,93</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -9,77</t>
+          <t>-16,08; -9,73</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 17,86</t>
+          <t>-1,89; 18,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,95</t>
+          <t>18,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,08</t>
+          <t>22,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>20,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 14,49</t>
+          <t>-2,85; 14,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 9,83</t>
+          <t>-7,88; 8,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 24,55</t>
+          <t>10,13; 26,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 8,61</t>
+          <t>-10,03; 7,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 6,49</t>
+          <t>-10,69; 6,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 30,37</t>
+          <t>14,66; 29,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 8,3</t>
+          <t>-3,69; 8,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 4,97</t>
+          <t>-6,92; 5,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 25,1</t>
+          <t>14,96; 26,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 34,88</t>
+          <t>-5,59; 35,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 24,65</t>
+          <t>-16,21; 20,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,18; 61,92</t>
+          <t>21,3; 64,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 16,69</t>
+          <t>-16,45; 13,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 12,44</t>
+          <t>-17,42; 11,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,53; 58,96</t>
+          <t>23,87; 57,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 17,41</t>
+          <t>-6,79; 17,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 10,48</t>
+          <t>-13,03; 12,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,6; 53,49</t>
+          <t>27,28; 56,33</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-3,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-3,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 8,66</t>
+          <t>-4,64; 8,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 3,73</t>
+          <t>-9,84; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 3,28</t>
+          <t>-10,8; 3,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 11,82</t>
+          <t>-1,16; 10,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 0,79</t>
+          <t>-11,15; 1,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 2,48</t>
+          <t>-9,39; 2,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 7,73</t>
+          <t>-0,6; 8,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,14</t>
+          <t>-8,61; 0,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 0,93</t>
+          <t>-8,02; 1,33</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,6%</t>
+          <t>-7,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,78%</t>
+          <t>-5,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-6,19%</t>
+          <t>-6,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 19,75</t>
+          <t>-8,74; 18,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 8,14</t>
+          <t>-18,94; 7,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 7,63</t>
+          <t>-21,23; 7,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 21,46</t>
+          <t>-1,81; 19,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 1,48</t>
+          <t>-18,2; 2,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 4,3</t>
+          <t>-15,17; 4,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 14,9</t>
+          <t>-1,17; 16,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 0,21</t>
+          <t>-15,65; 1,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 1,78</t>
+          <t>-14,22; 2,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,31</t>
+          <t>10,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,45</t>
+          <t>-17,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 7,83</t>
+          <t>-7,09; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,94; -4,81</t>
+          <t>-18,91; -4,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 18,17</t>
+          <t>2,74; 18,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,32; -9,19</t>
+          <t>-24,62; -10,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,59; -28,7</t>
+          <t>-42,47; -28,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,03; -10,36</t>
+          <t>-24,81; -11,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -2,96</t>
+          <t>-14,75; -3,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,38; -19,34</t>
+          <t>-29,8; -19,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 1,21</t>
+          <t>-9,04; 0,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-25,13%</t>
+          <t>-25,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 20,51</t>
+          <t>-15,44; 19,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -12,68</t>
+          <t>-41,12; -12,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 48,08</t>
+          <t>5,91; 47,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,06; -14,21</t>
+          <t>-33,72; -15,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,99; -43,11</t>
+          <t>-59,45; -42,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,55; -15,8</t>
+          <t>-33,85; -16,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,12; -5,2</t>
+          <t>-25,03; -6,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,71; -35,85</t>
+          <t>-50,44; -35,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 2,18</t>
+          <t>-15,35; 1,3</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-18,29</t>
+          <t>-6,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,02</t>
+          <t>-0,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 3,96</t>
+          <t>-10,9; 4,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,87; 23,07</t>
+          <t>7,4; 22,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 16,39</t>
+          <t>-4,08; 13,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,38; -2,54</t>
+          <t>-17,3; -3,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 10,2</t>
+          <t>-3,31; 10,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,53; -5,32</t>
+          <t>-13,79; 1,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -1,46</t>
+          <t>-11,61; -1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,61</t>
+          <t>3,76; 14,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 2,04</t>
+          <t>-6,1; 4,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,25%</t>
+          <t>-11,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 10,44</t>
+          <t>-25,04; 10,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,7; 60,42</t>
+          <t>16,6; 59,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 42,11</t>
+          <t>-9,21; 35,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,96; -4,37</t>
+          <t>-27,07; -5,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 18,04</t>
+          <t>-5,07; 18,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -9,86</t>
+          <t>-21,82; 2,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,69; -3,0</t>
+          <t>-21,62; -2,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,75; 30,83</t>
+          <t>6,94; 29,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 3,65</t>
+          <t>-11,49; 10,06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>4,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 21,09</t>
+          <t>0,3; 19,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 6,92</t>
+          <t>-11,63; 6,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 16,66</t>
+          <t>-2,26; 15,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 19,14</t>
+          <t>-0,48; 18,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 0,29</t>
+          <t>-18,81; 0,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 11,69</t>
+          <t>-6,2; 11,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 16,27</t>
+          <t>2,42; 16,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,34; -0,25</t>
+          <t>-13,29; 0,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 12,19</t>
+          <t>-1,74; 10,48</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,47; 74,09</t>
+          <t>0,27; 63,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 24,14</t>
+          <t>-31,37; 20,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 56,37</t>
+          <t>-5,71; 56,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 45,96</t>
+          <t>-0,96; 43,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,4; 0,45</t>
+          <t>-35,06; 0,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 26,86</t>
+          <t>-11,46; 26,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,26; 42,65</t>
+          <t>5,79; 43,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,15; -0,58</t>
+          <t>-29,48; 1,54</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 32,18</t>
+          <t>-3,83; 28,28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>11,18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-6,64</t>
+          <t>-6,36</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>2,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 12,56</t>
+          <t>-5,22; 12,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 0,32</t>
+          <t>-16,77; 0,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,75; 19,59</t>
+          <t>3,15; 19,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -4,56</t>
+          <t>-21,38; -5,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-31,32; -14,29</t>
+          <t>-30,96; -15,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 0,72</t>
+          <t>-13,71; 1,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 1,43</t>
+          <t>-10,89; 1,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -10,24</t>
+          <t>-21,95; -10,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 7,95</t>
+          <t>-3,47; 8,11</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-9,67%</t>
+          <t>-9,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 33,04</t>
+          <t>-11,23; 31,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 0,99</t>
+          <t>-36,14; 0,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8,08; 51,42</t>
+          <t>6,42; 49,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-28,85; -7,24</t>
+          <t>-29,72; -7,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,45; -22,18</t>
+          <t>-43,14; -22,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 1,16</t>
+          <t>-19,13; 1,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 2,48</t>
+          <t>-18,82; 2,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,77; -18,74</t>
+          <t>-36,76; -18,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 14,69</t>
+          <t>-6,0; 15,27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>-5,27</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>-0,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 1,47</t>
+          <t>-9,31; 1,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -1,86</t>
+          <t>-13,09; -1,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 9,34</t>
+          <t>-2,06; 9,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 1,23</t>
+          <t>-9,69; 1,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -2,02</t>
+          <t>-13,26; -2,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 27,65</t>
+          <t>-10,34; 0,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,26</t>
+          <t>-7,79; 0,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-11,24; -3,48</t>
+          <t>-11,54; -3,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 23,77</t>
+          <t>-4,58; 2,91</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>-9,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>-1,78%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 3,3</t>
+          <t>-19,61; 3,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,72; -4,29</t>
+          <t>-26,9; -4,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 21,52</t>
+          <t>-4,6; 21,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 2,33</t>
+          <t>-16,03; 2,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,12; -3,8</t>
+          <t>-22,32; -4,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 51,76</t>
+          <t>-17,28; 0,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -0,43</t>
+          <t>-14,62; 0,19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,28; -7,23</t>
+          <t>-21,23; -7,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 46,76</t>
+          <t>-8,56; 5,82</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11,22</t>
+          <t>-7,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-7,0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>-7,32</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 8,44</t>
+          <t>-1,38; 8,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,54; -1,65</t>
+          <t>-11,28; -1,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 39,1</t>
+          <t>-12,05; -1,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,62</t>
+          <t>-2,5; 7,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,76</t>
+          <t>-9,62; 1,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -1,43</t>
+          <t>-12,33; -2,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,53</t>
+          <t>-0,57; 6,7</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -2,2</t>
+          <t>-9,03; -2,03</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 25,87</t>
+          <t>-10,37; -3,62</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>-19,84%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-12,97%</t>
+          <t>-14,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>-17,12%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 23,44</t>
+          <t>-3,45; 24,87</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,86; -3,81</t>
+          <t>-28,31; -3,88</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 104,59</t>
+          <t>-30,01; -5,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 17,11</t>
+          <t>-4,9; 18,01</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 1,44</t>
+          <t>-19,81; 2,43</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-22,04; -3,34</t>
+          <t>-24,32; -5,08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 16,05</t>
+          <t>-1,19; 16,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-20,99; -5,32</t>
+          <t>-20,0; -4,84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 61,25</t>
+          <t>-23,48; -8,9</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-4,12</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,93</t>
+          <t>-1,03; 3,98</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -1,24</t>
+          <t>-5,88; -1,12</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,56; 17,79</t>
+          <t>0,49; 5,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,07</t>
+          <t>-5,27; -0,42</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -6,64</t>
+          <t>-11,41; -6,74</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,95</t>
+          <t>-6,22; -1,75</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,96</t>
+          <t>-2,44; 1,08</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -4,78</t>
+          <t>-8,19; -4,72</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,1</t>
+          <t>-2,34; 1,15</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-4,09%</t>
+          <t>-7,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>-1,23%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 9,51</t>
+          <t>-2,37; 9,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -2,98</t>
+          <t>-13,47; -2,68</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5,88; 41,8</t>
+          <t>1,13; 13,2</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,14</t>
+          <t>-8,99; -0,74</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -11,82</t>
+          <t>-19,85; -12,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 10,58</t>
+          <t>-10,65; -3,17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,93</t>
+          <t>-4,77; 2,21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -9,73</t>
+          <t>-16,04; -9,52</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 18,35</t>
+          <t>-4,61; 2,38</t>
         </is>
       </c>
     </row>
